--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Programkurser olankade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olankade'!$A$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$116</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,17 +1724,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Examensarbete i ämne 1 eller 2` (30 hp); rad: - Examensarbete i ämne 1 eller 2, 30 hp</t>
+          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2426,24 +2426,24 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2453,17 +2453,17 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
+          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMHTA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,24 +2804,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Bullet beskriver val mellan flera kurser</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Eller Examensarbete för Magisterexamen i Turismvetenskap` (15 hp); rad: - Eller Examensarbete för Magisterexamen i Turismvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2831,24 +2831,24 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Valbar Inriktningskurs` (15hp); rad: - Valbar Inriktningskurs, 15hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2858,24 +2858,24 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SMHTA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2885,24 +2885,24 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Eller Examensarbete för Magisterexamen i Turismvetenskap` (15 hp); rad: - Eller Examensarbete för Magisterexamen i Turismvetenskap, 15 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SMHTA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2912,24 +2912,24 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Studenterna väljer valfria kurser, i valfritt ämne nationellt eller internationellt, i enlighet med eget intresse och i samråd med programansvarig. Ett antal valfria kurser om` (30 hp); rad: - Studenterna väljer valfria kurser, i valfritt ämne nationellt eller internationellt, i enlighet med eget intresse och i samråd med programansvarig. Ett antal valfria kurser om, 30 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3160,19 +3160,19 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3511,19 +3511,19 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3538,19 +3538,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3560,130 +3560,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
-        </is>
-      </c>
-      <c r="E119" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E120" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E120"/>
+  <autoFilter ref="A1:E116"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3915,14 +3807,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$116</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2794,7 +2794,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SMHTA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2804,17 +2804,17 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bullet beskriver val mellan flera kurser</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Eller Examensarbete för Magisterexamen i Turismvetenskap` (15 hp); rad: - Eller Examensarbete för Magisterexamen i Turismvetenskap, 15 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMHTA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3469,7 +3469,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3479,17 +3479,17 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -3547,35 +3547,8 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E116"/>
+  <autoFilter ref="A1:E115"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3805,8 +3778,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$115</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -499,7 +499,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KAPSG</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,17 +509,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Programtext `Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` ≠ kursplanens namn `Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` (kurskod `GLP2NK`); rad: - [[GLP2NK|Konceptutveckling inom medieproduktion för Ljud- och musikproduktion]], 7,5 hp</t>
+          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KAPSG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
+          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
+          <t>`7` (5 hp); rad: - 7, 5 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -580,7 +580,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`7` (5 hp); rad: - 7, 5 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -622,12 +622,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
+          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>Programtext `Utveckling och lärande för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Utveckling och lärande för ämneslärare årskurs 7-9 - AIL` (kurskod `GPG3AE`); rad: - &lt;a class="no-graph" href="GPG3AE"&gt;Utveckling och lärande för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Utveckling och lärande för ämneslärare årskurs 7-9 - AIL` (kurskod `GPG3AE`); rad: - &lt;a class="no-graph" href="GPG3AE"&gt;Utveckling och lärande för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL` (kurskod `APG2AB`); rad: - &lt;a class="no-graph" href="APG2AB"&gt;Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL` (kurskod `APG2AB`); rad: - &lt;a class="no-graph" href="APG2AB"&gt;Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
+          <t>Programtext `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AIH237`); rad: - [[AIH237|Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9]], 15 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AIH237`); rad: - [[AIH237|Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9]], 15 hp</t>
+          <t>Programtext `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`); rad: - &lt;a class="no-graph" href="AMD239"&gt;Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`); rad: - &lt;a class="no-graph" href="AMD239"&gt;Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9&lt;/a&gt;, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - [[GPG3CK|Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6]], 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - [[GPG3CK|Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
+          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2470,7 +2470,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2777,17 +2777,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -3425,12 +3425,12 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -3520,35 +3520,8 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E115"/>
+  <autoFilter ref="A1:E114"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3776,8 +3749,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>HDMFA</t>
+          <t>KFTKG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,17 +482,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Programtext `Samhällsvetenskapliga metoder III – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder III - inriktning statsvetenskap` (kurskod `ASK289`); rad: - [[ASK289|Samhällsvetenskapliga metoder III – inriktning statsvetenskap]], 15 hp</t>
+          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HDMFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
+          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
+          <t>`7` (5 hp); rad: - 7, 5 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`7` (5 hp); rad: - 7, 5 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,12 +595,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
+          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1049,24 +1049,24 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Utveckling och lärande för ämneslärare årskurs 7-9 - AIL` (kurskod `GPG3AE`); rad: - &lt;a class="no-graph" href="GPG3AE"&gt;Utveckling och lärande för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL` ≠ kursplanens namn `Bedömning och betygssättning för ämneslärare årskurs 7-9 - AIL` (kurskod `APG2AB`); rad: - &lt;a class="no-graph" href="APG2AB"&gt;Bedömning och betygssättning för ämneslärare årskurs 7–9 - AIL&lt;/a&gt;, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AIH237`); rad: - [[AIH237|Examensarbete i idrott och hälsa för ämneslärarexamen inriktning grundskolans årskurs 7–9]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` ≠ kursplanens namn `Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`); rad: - &lt;a class="no-graph" href="AMD239"&gt;Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1-6` (kurskod `GPG3CK`); rad: - [[GPG3CK|Skolväsendets historia och samhällsuppdrag - förskoleklass och grundskolan åk 1–6]], 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1265,24 +1265,24 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1292,24 +1292,24 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,24 +1940,24 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1967,24 +1967,24 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programtext `Skolväsendets historia och samhällsuppdrag – ämneslärare` ≠ kursplanens namn `Skolväsendets historia och samhällsuppdrag - ämneslärare` (kurskod `GPG32A`); rad: - [[GPG32A|Skolväsendets historia och samhällsuppdrag – ämneslärare]], 15 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2345,24 +2345,24 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2372,24 +2372,24 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,24 +2534,24 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2750,24 +2750,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,12 +2809,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2971,19 +2971,19 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,19 +3052,19 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3199,7 +3199,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,19 +3214,19 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3241,19 +3241,19 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3268,260 +3268,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Programtext `Samhällsvetenskapliga metoder I – inriktning statsvetenskap` ≠ kursplanens namn `Samhällsvetenskapliga metoder I - inriktning statsvetenskap` (kurskod `GSK2PT`); rad: - [[GSK2PT|Samhällsvetenskapliga metoder I – inriktning statsvetenskap]], 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E112" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
-        </is>
-      </c>
-      <c r="E113" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E114"/>
+  <autoFilter ref="A1:E105"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3731,24 +3488,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`7` (5 hp); rad: - 7, 5 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
+          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,12 +1000,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,17 +2156,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,12 +2269,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2524,7 +2524,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2534,17 +2534,17 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3182,17 +3182,17 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3250,35 +3250,8 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E105"/>
+  <autoFilter ref="A1:E104"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3486,8 +3459,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -487,19 +487,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Grundläggande filmproduktion för Manus för film och TV` (15 hp); rad: - Grundläggande filmproduktion för Manus för film och TV, 15 hp</t>
+          <t>`Magisterprojektets planering` (1 hp); rad: - Magisterprojektets planering, 1 hp</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>KFTKG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,19 +514,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Dokumentär metod för filmisk gestaltning` (7,5 hp); rad: - Dokumentär metod för filmisk gestaltning, 7,5 hp</t>
+          <t>`Den vidareutvecklade uppsatsplanen` (1 hp); rad: - Den vidareutvecklade uppsatsplanen, 1 hp</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTKG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -541,19 +541,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Magisterexamensarbete i Afrikanska studier` (15 hp); rad: - Magisterexamensarbete i Afrikanska studier, 15 hp</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp); rad: - Bistånd och utveckling i Afrika söder om Sahara, 7 hp</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -595,19 +595,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>`Egypten och medierna` (7 hp); rad: - Egypten och medierna, 7 hp</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -617,24 +617,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
+          <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp); rad: - Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik, 7 hp</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -649,19 +649,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Den nordafrikanska novellen` (7 hp); rad: - Den nordafrikanska novellen, 7 hp</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -676,19 +676,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Islam och muslimska samhällen i Afrika` (7 hp); rad: - Islam och muslimska samhällen i Afrika, 7 hp</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -703,19 +703,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp); rad: - Språk och nationalitet i afrikanska flerspråkliga länder, 7 hp</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -730,19 +730,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Södra Afrikas moderna historia` (7 hp); rad: - Södra Afrikas moderna historia, 7 hp</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`Afrikas horn` (7 hp); rad: - Afrikas horn, 7 hp</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -784,19 +784,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i musik­ och ljuddesign` (15 hp); rad: - Examensarbete för högskoleexamen i musik­ och ljuddesign, 15 hp</t>
+          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp); rad: - Fred och konflikt i Afrika: Internationell institutionell lag, 7 hp</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Västafrika sedan 1800-talet` (7 hp); rad: - Västafrika sedan 1800-talet, 7 hp</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>Programtext `Afrikanska samhällen i förändring` ≠ kursplanens namn `Afrikanska studier: Afrikanska samhällen i förändring` (kurskod `AS3022`); rad: - [[AS3022|Afrikanska samhällen i förändring]], 12 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>Programtext `Religion och politik i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Religion och politik i afrikanska samhällen` (kurskod `AS3023`); rad: - [[AS3023|Religion och politik i afrikanska samhällen]], 9 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>Programtext `Utbildning och förändring i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Utbildning och förändring i afrikanska samhällen` (kurskod `AS3021`); rad: - [[AS3021|Utbildning och förändring i afrikanska samhällen]], 8 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -914,24 +914,24 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>Programtext `Litteratur och politik i det samtida Afrika` ≠ kursplanens namn `Afrikanska studier: Litteratur och politik i det samtida Afrika` (kurskod `AS3017`); rad: - [[AS3017|Litteratur och politik i det samtida Afrika]], 7 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>Programtext `Ekonomisk utveckling i Afrika, en introduktion` ≠ kursplanens namn `Afrikanska studier: Ekonomisk utveckling i Afrika, en introduktion` (kurskod `AS3019`); rad: - [[AS3019|Ekonomisk utveckling i Afrika, en introduktion]], 7 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>Programtext `Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` ≠ kursplanens namn `Afrikanska studier: Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` (kurskod `AS3014`); rad: - [[AS3014|Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv]], 7hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning` (7,5 hp); rad: - Vid Högskolan Dalarna är examensarbetet en angelägenhet för hela utbildningen och inte enbart de specifika examensarbeteskurserna. Förmågan till vetenskapligt tänkande och skrivande utvecklas successivt under utbildningen, men fokuseras i kärnkursen Vetenskapsteori och utbildningsvetenskaplig forskning, 7,5 hp</t>
+          <t>Programtext `Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` ≠ kursplanens namn `Afrikanska studier: Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` (kurskod `AS3018`); rad: - [[AS3018|Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara]], 7 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1076,24 +1076,24 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1130,24 +1130,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1157,24 +1157,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
+          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1184,24 +1184,24 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1211,24 +1211,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1319,24 +1319,24 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Examensarbete för högskoleexamen i musik­ och ljuddesign` ≠ kursplanens namn `Examensarbete för högskoleexamen i musik- och ljuddesign` (kurskod `LP1032`); rad: - [[LP1032|Examensarbete för högskoleexamen i musik­ och ljuddesign]], 15 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning I` (30 hp); rad: - Ämne 1 med didaktisk inriktning I, 30 hp</t>
+          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning II` (30 hp); rad: - Ämne 1 med didaktisk inriktning II, 30 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Ämne 1 med didaktisk inriktning III` (30 hp); rad: - Ämne 1 med didaktisk inriktning III, 30 hp</t>
+          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning I` (30 hp); rad: - Ämne 2 med didaktisk inriktning I, 30 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning II` (30 hp); rad: - Ämne 2 med didaktisk inriktning II, 30 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Ämne 2 med didaktisk inriktning III` (30 hp); rad: - Ämne 2 med didaktisk inriktning III, 30 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt` (30 hp); rad: - En valideringskurs inom verksamhetsförlagd utbildning erbjuds (Verksamhetsförlagd utbildning – VAL, 7,5 hp) som, om den godkänns, ligger till grund för validering av kurserna Verksamhetsförlagd utbildning 1-3, totalt, 30 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Valfri kurs` (7,5 hp); rad: - Valfri kurs, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Obligatoriska kurser` (30 hp); rad: - Obligatoriska kurser, 30 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2507,24 +2507,24 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3187,19 +3187,19 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>STMGG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3214,44 +3214,152 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>SSHVG</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
           <t>STMGG</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>STMGG</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Utbildningsplan</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
         <is>
           <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E104"/>
+  <autoFilter ref="A1:E108"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3459,6 +3567,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,24 +833,24 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Programtext `Afrikanska samhällen i förändring` ≠ kursplanens namn `Afrikanska studier: Afrikanska samhällen i förändring` (kurskod `AS3022`); rad: - [[AS3022|Afrikanska samhällen i förändring]], 12 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -860,24 +860,24 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Programtext `Religion och politik i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Religion och politik i afrikanska samhällen` (kurskod `AS3023`); rad: - [[AS3023|Religion och politik i afrikanska samhällen]], 9 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -887,24 +887,24 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Programtext `Utbildning och förändring i afrikanska samhällen` ≠ kursplanens namn `Afrikanska studier: Utbildning och förändring i afrikanska samhällen` (kurskod `AS3021`); rad: - [[AS3021|Utbildning och förändring i afrikanska samhällen]], 8 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -919,19 +919,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Programtext `Litteratur och politik i det samtida Afrika` ≠ kursplanens namn `Afrikanska studier: Litteratur och politik i det samtida Afrika` (kurskod `AS3017`); rad: - [[AS3017|Litteratur och politik i det samtida Afrika]], 7 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -941,24 +941,24 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Programtext `Ekonomisk utveckling i Afrika, en introduktion` ≠ kursplanens namn `Afrikanska studier: Ekonomisk utveckling i Afrika, en introduktion` (kurskod `AS3019`); rad: - [[AS3019|Ekonomisk utveckling i Afrika, en introduktion]], 7 hp</t>
+          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -968,24 +968,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Programtext `Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` ≠ kursplanens namn `Afrikanska studier: Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv` (kurskod `AS3014`); rad: - [[AS3014|Internationell hälsa med fokus på nutrition i ett genus- och ekonomiskt perspektiv]], 7hp</t>
+          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -995,24 +995,24 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Programtext `Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` ≠ kursplanens namn `Afrikanska studier: Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara` (kurskod `AS3018`); rad: - [[AS3018|Det urbana rummet och urbaniseringspolitik i Afrika söder om Sahara]], 7 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,19 +1081,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1103,24 +1103,24 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
+          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,19 +1270,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete för högskoleexamen i musik­ och ljuddesign` ≠ kursplanens namn `Examensarbete för högskoleexamen i musik- och ljuddesign` (kurskod `LP1032`); rad: - [[LP1032|Examensarbete för högskoleexamen i musik­ och ljuddesign]], 15 hp</t>
+          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1346,24 +1346,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,24 +1400,24 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1562,24 +1562,24 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1589,24 +1589,24 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur` ≠ kursplanens namn `Svenska 1 för grundlärare F-3` (kurskod `GSV2ZV`); rad: - &lt;a class="no-graph" href="GSV2ZV"&gt;Svenska 1 för grundlärare F-3: Barns språkutveckling, språklig variation samt barn- och ungdomslitteratur&lt;/a&gt;, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,24 +1670,24 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Programtext `Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning` ≠ kursplanens namn `Svenska 2 för grundlärare F-3` (kurskod `GSV2ZW`); rad: - &lt;a class="no-graph" href="GSV2ZW"&gt;Svenska 2 för grundlärare F-3: Läs- och skrivutveckling och läs- och skrivundervisning&lt;/a&gt;, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1697,24 +1697,24 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1724,24 +1724,24 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1751,24 +1751,24 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1778,24 +1778,24 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1805,24 +1805,24 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1832,24 +1832,24 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1859,24 +1859,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1886,24 +1886,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1913,24 +1913,24 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2038,7 +2038,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2048,24 +2048,24 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2075,24 +2075,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2102,24 +2102,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2129,24 +2129,24 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2156,24 +2156,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2183,24 +2183,24 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2210,24 +2210,24 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2264,24 +2264,24 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2291,24 +2291,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,19 +2404,19 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2431,19 +2431,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2615,24 +2615,24 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Programtext `Examensarbete` ≠ kursplanens namn `Tyska: Examensarbete` (kurskod `TY2007`); rad: - &lt;a class="no-graph" href="TY2007"&gt;Examensarbete&lt;/a&gt;, 15 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,19 +2647,19 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2674,19 +2674,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2728,19 +2728,19 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2755,19 +2755,19 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2782,19 +2782,19 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2809,19 +2809,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2863,19 +2863,19 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2890,19 +2890,19 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2917,19 +2917,19 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2998,19 +2998,19 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3025,19 +3025,19 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3052,314 +3052,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E108"/>
+  <autoFilter ref="A1:E97"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3553,28 +3256,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande i förskoleklass och grundskolans åk 1–3` ≠ kursplanens namn `Utveckling och lärande i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG3CF`); rad: - [[GPG3CF|Utveckling och lärande i förskoleklass och grundskolans åk 1–3]], 15 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3` ≠ kursplanens namn `Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1-3 (varav 7,5 hp VFU)` (kurskod `GPG2M9`); rad: - [[GPG2M9|Sociala relationer, konflikter och makt i förskoleklass och grundskolan åk 1–3]], 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1373,24 +1373,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1400,17 +1400,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1643,24 +1643,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1670,17 +1670,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1994,24 +1994,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2021,24 +2021,24 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2647,12 +2647,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2912,12 +2912,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2944,19 +2944,19 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -3007,62 +3007,8 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E97"/>
+  <autoFilter ref="A1:E95"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3252,10 +3198,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -487,7 +487,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>`Magisterprojektets planering` (1 hp); rad: - Magisterprojektets planering, 1 hp</t>
+          <t>`Magisterprojektets planering` (1 hp)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>`Den vidareutvecklade uppsatsplanen` (1 hp); rad: - Den vidareutvecklade uppsatsplanen, 1 hp</t>
+          <t>`Den vidareutvecklade uppsatsplanen` (1 hp)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>`Magisterexamensarbete i Afrikanska studier` (15 hp); rad: - Magisterexamensarbete i Afrikanska studier, 15 hp</t>
+          <t>`Magisterexamensarbete i Afrikanska studier` (15 hp)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp); rad: - Bistånd och utveckling i Afrika söder om Sahara, 7 hp</t>
+          <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>`Egypten och medierna` (7 hp); rad: - Egypten och medierna, 7 hp</t>
+          <t>`Egypten och medierna` (7 hp)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp); rad: - Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik, 7 hp</t>
+          <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp)</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>`Den nordafrikanska novellen` (7 hp); rad: - Den nordafrikanska novellen, 7 hp</t>
+          <t>`Den nordafrikanska novellen` (7 hp)</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>`Islam och muslimska samhällen i Afrika` (7 hp); rad: - Islam och muslimska samhällen i Afrika, 7 hp</t>
+          <t>`Islam och muslimska samhällen i Afrika` (7 hp)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp); rad: - Språk och nationalitet i afrikanska flerspråkliga länder, 7 hp</t>
+          <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp)</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>`Södra Afrikas moderna historia` (7 hp); rad: - Södra Afrikas moderna historia, 7 hp</t>
+          <t>`Södra Afrikas moderna historia` (7 hp)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>`Afrikas horn` (7 hp); rad: - Afrikas horn, 7 hp</t>
+          <t>`Afrikas horn` (7 hp)</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp); rad: - Fred och konflikt i Afrika: Internationell institutionell lag, 7 hp</t>
+          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp)</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>`Västafrika sedan 1800-talet` (7 hp); rad: - Västafrika sedan 1800-talet, 7 hp</t>
+          <t>`Västafrika sedan 1800-talet` (7 hp)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp); rad: - Digitalefterbearbetning av ljud och bild, 15 hp</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp); rad: - Konceptutveckling inom medieproduktion i Ljud- och musikproduktion, 7,5 hp</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp); rad: - Arbetsplatsförlagd utbildning för medieproduktion, 15 hp</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp)</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`); rad: - [[LP1072|Produktionsprocesser och -villkor inom musikproduktion]], 7,5 hp</t>
+          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`)</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp); rad: - Audioteknologi I, 7,5 hp</t>
+          <t>`Audioteknologi I` (7,5 hp)</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp); rad: - Audioteknologi II, 7,5 hp</t>
+          <t>`Audioteknologi II` (7,5 hp)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp); rad: - Introduktion till Musik- och ljuddesign, 7,5 hp</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp); rad: - Ljudskapande och ljudsyntes, 7,5 hp</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp); rad: - Vår tids musik och musikliv, 7,5 hp</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp); rad: - Företagsekonomi för musikbranschen, 7,5 hp</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp); rad: - Musikbranschen, 7,5 hp</t>
+          <t>`Musikbranschen` (7,5 hp)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp); rad: - Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp); rad: - Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL, 7,5 hp</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp); rad: - _Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9, 15 hp</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp); rad: - Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3, 15 hp</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`); rad: - [[APG244|Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`); rad: - &lt;a class="no-graph" href="GEN2BJ"&gt;Engelska för grundlärare åk F-3&lt;/a&gt;, 15 hp</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp); rad: - Utveckling och lärande för ämneslärare inriktning åk 7-9, 15 hp</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp); rad: - Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan, 15 hp</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp); rad: - Utveckling och lärande - ämneslärare, 15 hp</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp); rad: - Sociala relationer, konflikter och makt - ämneslärare, 7,5 hp</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp); rad: - Utvärdering och utvecklingsarbete för ämneslärare, 7,5 hp</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp); rad: - Verksamhetsförlagd utbildning - ämneslärare, 15 hp</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`); rad: - [[GPG2Z7|Skolans samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`); rad: - [[GPG3BE|Didaktik och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`); rad: - [[GPG2Z4|Utveckling och lärande]], 7,5 hp</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`); rad: - [[GPG2Z6|Sociala relationer och konflikthantering]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`); rad: - [[APG28M|Vetenskapsteori och utbildningsvetenskaplig forskning]], 7,5 hp</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`); rad: - [[GPG3FU|Utvärdering och utvecklingsarbete]], 7,5 hp</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`); rad: - [[GPG3FV|Självständigt arbete]], 7,5 hp</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`); rad: - [[GPG3FS|Verksamhetsförlagd utbildning 1]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`); rad: - [[GPG3FT|Verksamhetsförlagd utbildning 2]], 15 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`); rad: - [[APG2BK|Verksamhetsförlagd utbildning 3]], 7,5 hp</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -1918,7 +1918,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`); rad: - [[GPG33F|Didaktik och bedömning]], 7,5 hp</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`); rad: - [[GPG33D|Utveckling, lärande och ledarskap]], 7,5 hp</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`); rad: - [[GPG33E|Sociala relationer, skolans historiska utveckling och samhällsuppdrag]], 7,5 hp</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp); rad: - Evenemangsturism, 7,5 hp</t>
+          <t>`Evenemangsturism` (7,5 hp)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp); rad: - Makroekonomi introduktion, 7,5 hp</t>
+          <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp); rad: - Mikroekonomi introduktion, 7,5 hp</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp); rad: - Mikroekonomi fortsättningskurs, 7,5 hp</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp); rad: - Makroekonomi fortsättning, 7,5 hp</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp); rad: - Entreprenörskap - entreprenörskapets villkor och särart, 7,5 hp</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp); rad: - Förhandlings  försäljnings  och dialogkonst, 7,5 hp</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp); rad: - Studier i Internationell Human Resource Management, 15 hp</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp); rad: - Avancerad mikroteori, 7,5 hp</t>
+          <t>`Avancerad mikroteori` (7,5 hp)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp); rad: - Samhällsekonomisk utvärdering av offentliga projekt, 7,5 hp</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp); rad: - Arbetsrätt i personalarbetets praktik, 15 hp</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp); rad: - Grunder i personalekonomisk styrning, 15 hp</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp); rad: - Personalarbete med praktik, 15 hp</t>
+          <t>`Personalarbete med praktik` (15 hp)</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmarknad i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp); rad: - Arbetsmiljökunskap i ett jämförande internationellt perspektiv, 7,5 hp</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp); rad: - Examensarbete inom arbetsvetenskap, 15 hp</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp); rad: - Forskningsprocess och analysmetoder, 7,5 hp</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp); rad: - Komplexa arbetsorganisationer, 7,5 hp</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp); rad: - Komplexa sociala processer i arbetslivet, 7,5 hp</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp); rad: - Vetenskap och metod, 7,5 hp</t>
+          <t>`Vetenskap och metod` (7,5 hp)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp); rad: - Inriktning sociologi II, 30 hp</t>
+          <t>`Inriktning sociologi II` (30 hp)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp); rad: - Examensarbete för högskoleexamen i Sociologi, 7,5 hp</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp); rad: - Makt och samhälle, 7,5 hp</t>
+          <t>`Makt och samhälle` (7,5 hp)</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp); rad: - Samhällsvetenskapliga metoder I, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp); rad: - Inriktning statsvetenskap II, 30 hp</t>
+          <t>`Inriktning statsvetenskap II` (30 hp)</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp); rad: - Inriktning sociologi III, 30 hp</t>
+          <t>`Inriktning sociologi III` (30 hp)</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp); rad: - Examensarbete för kandidatexamen i sociologi, 15 hp</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp); rad: - Fördjupningskurs i sociologisk teori, 7,5 hp</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp); rad: - Samhällsvetenskapliga metoder II, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp); rad: - Inriktning statsvetenskap III, 30 hp</t>
+          <t>`Inriktning statsvetenskap III` (30 hp)</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp); rad: - Samhällsvetenskapliga metoder II inriktning statsvetenskap, 7,5 hp</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp); rad: - Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om, 30 hp</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp); rad: - Festival och Event Management, 7,5 hp</t>
+          <t>`Festival och Event Management` (7,5 hp)</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp); rad: - Turismstudier utomlands, 30 hp</t>
+          <t>`Turismstudier utomlands` (30 hp)</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp); rad: - Kvantitativa forskningsmetoder, 7,5 hp</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$E$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>`Magisterprojektets planering` (1 hp)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>`Den vidareutvecklade uppsatsplanen` (1 hp)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>`Magisterexamensarbete i Afrikanska studier` (15 hp)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp)</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>`Egypten och medierna` (7 hp)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>`Den nordafrikanska novellen` (7 hp)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>`Islam och muslimska samhällen i Afrika` (7 hp)</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp)</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>`Södra Afrikas moderna historia` (7 hp)</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -752,15 +824,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>`Afrikas horn` (7 hp)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -779,15 +857,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp)</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -806,15 +890,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2014-11-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>`Västafrika sedan 1800-talet` (7 hp)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -833,15 +923,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2014-03-19</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>`Digitalefterbearbetning av ljud och bild` (15 hp)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
@@ -860,15 +960,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -887,15 +997,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -914,15 +1034,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -941,15 +1071,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>`Audioteknologi I` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -968,15 +1108,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>`Audioteknologi II` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -995,15 +1145,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1022,15 +1182,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1049,15 +1219,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>`Vår tids musik och musikliv` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1076,15 +1256,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1103,15 +1293,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>`Musikbranschen` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1130,15 +1330,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1157,15 +1363,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1184,15 +1396,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1211,15 +1429,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1238,15 +1462,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1265,15 +1495,25 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1292,15 +1532,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2020-12-17</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1319,15 +1569,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1346,15 +1606,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1373,15 +1643,25 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1400,15 +1680,25 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1427,15 +1717,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1454,15 +1754,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1481,15 +1791,25 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1508,15 +1828,25 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1535,15 +1865,25 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1562,15 +1902,25 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1589,15 +1939,25 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1616,15 +1976,25 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1643,15 +2013,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1670,15 +2046,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1697,15 +2079,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1724,15 +2112,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1751,15 +2145,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1778,15 +2178,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1805,15 +2211,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1832,15 +2244,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1859,15 +2277,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1886,15 +2310,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1913,15 +2343,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1940,15 +2376,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1967,15 +2409,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -1994,15 +2442,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
@@ -2021,15 +2475,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
@@ -2048,15 +2508,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2012-05-02</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>`Evenemangsturism` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
@@ -2075,15 +2541,25 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2102,15 +2578,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2129,15 +2615,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2156,15 +2652,25 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>`Makroekonomi fortsättning` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2183,15 +2689,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2210,15 +2726,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
@@ -2237,15 +2759,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
@@ -2264,15 +2792,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
@@ -2291,15 +2829,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>`Avancerad mikroteori` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
@@ -2318,15 +2862,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
@@ -2345,15 +2895,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2372,15 +2928,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2399,15 +2961,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>`Personalarbete med praktik` (15 hp)</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2426,15 +2994,21 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2453,15 +3027,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2480,15 +3060,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2507,15 +3093,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2534,15 +3126,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2561,15 +3159,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2588,15 +3192,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>`Vetenskap och metod` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2615,15 +3225,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>`Inriktning sociologi II` (30 hp)</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2642,15 +3258,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2669,15 +3291,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>`Makt och samhälle` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2696,15 +3324,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2723,15 +3357,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>`Inriktning statsvetenskap II` (30 hp)</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2750,15 +3390,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>`Inriktning sociologi III` (30 hp)</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2777,15 +3423,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2804,15 +3456,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2831,15 +3489,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2858,15 +3522,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>`Inriktning statsvetenskap III` (30 hp)</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2885,15 +3555,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2912,15 +3588,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>2021-06-16</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
           <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -2939,15 +3621,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>`Festival och Event Management` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -2966,15 +3658,25 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
           <t>`Turismstudier utomlands` (30 hp)</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -2993,211 +3695,221 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>2017-11-15</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
           <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E95"/>
+  <autoFilter ref="A1:G95"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1024,7 +1024,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Programtext `Produktionsprocesser och -villkor inom musikproduktion` ≠ kursplanens namn `Produktionsprocesser och - villkor inom musikproduktion` (kurskod `LP1072`)</t>
+          <t>`Audioteknologi I` (7,5 hp)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp)</t>
+          <t>`Audioteknologi II` (7,5 hp)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp)</t>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp)</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
+          <t>`Musikbranschen` (7,5 hp)</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1283,7 +1283,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1293,14 +1293,10 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -1308,12 +1304,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp)</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1337,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1374,7 +1370,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1407,7 +1403,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1440,7 +1436,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1452,7 +1448,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,10 +1458,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
+          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1606,27 +1606,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1976,27 +1976,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
+          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2020,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
+          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2057,7 +2053,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
+          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2090,7 +2086,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
+          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2123,7 +2119,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
+          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2156,7 +2152,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
+          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2189,7 +2185,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
+          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2222,7 +2218,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2255,7 +2251,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2288,7 +2284,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
+          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2321,7 +2317,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
+          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2354,7 +2350,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
+          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2387,7 +2383,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
+          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2399,7 +2395,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2409,23 +2405,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
+          <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2449,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp)</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2465,7 +2461,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2475,7 +2471,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2486,19 +2482,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
+          <t>`Evenemangsturism` (7,5 hp)</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,10 +2504,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2012-05-02</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp)</t>
+          <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp)</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp)</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp)</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2689,14 +2689,10 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -2704,12 +2700,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2733,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -2749,7 +2745,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2759,10 +2755,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>2017-09-14</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -2770,19 +2770,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2792,14 +2792,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
+          <t>2020-10-07</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -2807,12 +2803,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
+          <t>`Avancerad mikroteori` (7,5 hp)</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2836,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp)</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -2852,7 +2848,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2862,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2873,12 +2869,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2902,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -2939,7 +2935,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
+          <t>`Personalarbete med praktik` (15 hp)</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -2972,7 +2968,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp)</t>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -3005,7 +3001,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -3038,7 +3034,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -3071,7 +3067,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -3104,7 +3100,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -3137,7 +3133,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -3170,7 +3166,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
+          <t>`Vetenskap och metod` (7,5 hp)</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -3182,7 +3178,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3192,7 +3188,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3203,12 +3199,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp)</t>
+          <t>`Inriktning sociologi II` (30 hp)</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3232,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp)</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -3269,7 +3265,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
+          <t>`Makt och samhälle` (7,5 hp)</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
@@ -3302,7 +3298,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp)</t>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -3335,7 +3331,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
+          <t>`Inriktning statsvetenskap II` (30 hp)</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -3368,7 +3364,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp)</t>
+          <t>`Inriktning sociologi III` (30 hp)</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -3401,7 +3397,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp)</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
@@ -3434,7 +3430,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -3467,7 +3463,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -3500,7 +3496,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
+          <t>`Inriktning statsvetenskap III` (30 hp)</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -3533,7 +3529,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap III` (30 hp)</t>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
@@ -3561,12 +3557,12 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -3578,7 +3574,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3588,23 +3584,27 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
+          <t>`Festival och Event Management` (7,5 hp)</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>`Festival och Event Management` (7,5 hp)</t>
+          <t>`Turismstudier utomlands` (30 hp)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>`Turismstudier utomlands` (30 hp)</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
@@ -3682,45 +3682,8 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G95"/>
+  <autoFilter ref="A1:G94"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -3908,8 +3871,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$G$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$H$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +478,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Förslag</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Länk</t>
         </is>
       </c>
@@ -505,10 +511,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>`Magisterprojektets planering` (1 hp)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+          <t>`Magisterexamensarbete i Afrikanska studier` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -538,10 +545,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>`Den vidareutvecklade uppsatsplanen` (1 hp)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+          <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -571,10 +579,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>`Magisterexamensarbete i Afrikanska studier` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          <t>`Egypten och medierna` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -604,10 +613,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>`Bistånd och utveckling i Afrika söder om Sahara` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+          <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -637,10 +647,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>`Egypten och medierna` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+          <t>`Den nordafrikanska novellen` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -670,10 +681,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>`Egyptisk–sudanesiska relationer: Vattenresursernas geopolitik` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -703,10 +715,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Den nordafrikanska novellen` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+          <t>`Södra Afrikas moderna historia` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -736,10 +749,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Islam och muslimska samhällen i Afrika` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+          <t>`Afrikas horn` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -769,10 +783,11 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Språk och nationalitet i afrikanska flerspråkliga länder` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -802,10 +817,11 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Södra Afrikas moderna historia` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+          <t>`Västafrika sedan 1800-talet` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -830,15 +846,20 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Afrikas horn` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          <t>`Magisterprojektets planering` (1 hp)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>`Afrikanska studier: Forskningsprojektets planering` (kurskod `AS3024`)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -863,15 +884,20 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+          <t>`Den vidareutvecklade uppsatsplanen` (1 hp)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>`Afrikanska studier: Den vidareutvecklade forskningsplanen` (kurskod `AS3020`)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -896,15 +922,20 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Västafrika sedan 1800-talet` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+          <t>`Islam och muslimska samhällen i Afrika` (7 hp)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>`Afrikanska studier: Islam och islamiska samhällen i Afrika` (kurskod `AS3008`)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
         </is>
@@ -933,7 +964,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -941,7 +972,12 @@
           <t>`Digitalefterbearbetning av ljud och bild` (15 hp)</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>`Digital efterbearbetning av ljud och bild` (kurskod `GBQ2AY`)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
@@ -970,7 +1006,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -978,7 +1014,12 @@
           <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>`Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` (kurskod `GLP2NK`)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1007,7 +1048,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1015,7 +1056,12 @@
           <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>`Arbetsplatsförlagd utbildning i medieproduktion` (kurskod `GLP32S`)</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
@@ -1052,7 +1098,8 @@
           <t>`Audioteknologi I` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1089,7 +1136,8 @@
           <t>`Audioteknologi II` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1126,7 +1174,8 @@
           <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1163,7 +1212,8 @@
           <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1200,7 +1250,8 @@
           <t>`Vår tids musik och musikliv` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1237,7 +1288,8 @@
           <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1274,7 +1326,8 @@
           <t>`Musikbranschen` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
@@ -1307,7 +1360,8 @@
           <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1340,7 +1394,8 @@
           <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1373,7 +1428,8 @@
           <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1406,7 +1462,8 @@
           <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1431,7 +1488,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1439,7 +1496,12 @@
           <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>`Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`)</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
@@ -1468,7 +1530,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1538,12 @@
           <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans årskurs 1-3 (inkl 7,5 hp VFU)` (kurskod `GPG3CH`)</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1505,7 +1572,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1513,7 +1580,12 @@
           <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `APG275`)</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1547,10 +1619,15 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3`</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1584,10 +1661,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Programtext `Engelska för grundlärare åk F-3` ≠ kursplanens namn `Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
+          <t>`Engelska för grundlärare åk F-3`</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>`Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
@@ -1624,7 +1706,8 @@
           <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1658,10 +1741,11 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1690,15 +1774,20 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1727,15 +1816,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1764,15 +1858,20 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
@@ -1806,10 +1905,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1843,10 +1943,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1875,15 +1976,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)` (kurskod `GPG3KB`)</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1912,15 +2018,20 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1949,15 +2060,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
@@ -1987,10 +2103,15 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Programtext `Skolans samhällsuppdrag` ≠ kursplanens namn `Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+          <t>`Skolans samhällsuppdrag`</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>`Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2020,10 +2141,15 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och ledarskap` ≠ kursplanens namn `Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+          <t>`Didaktik och ledarskap`</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2053,10 +2179,15 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling och lärande` ≠ kursplanens namn `Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+          <t>`Utveckling och lärande`</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>`Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2086,10 +2217,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer och konflikthantering` ≠ kursplanens namn `Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+          <t>`Sociala relationer och konflikthantering`</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>`Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2119,10 +2255,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Programtext `Vetenskapsteori och utbildningsvetenskaplig forskning` ≠ kursplanens namn `Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning`</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2152,10 +2293,15 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Programtext `Utvärdering och utvecklingsarbete` ≠ kursplanens namn `Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+          <t>`Utvärdering och utvecklingsarbete`</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2185,10 +2331,15 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Programtext `Självständigt arbete` ≠ kursplanens namn `Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+          <t>`Självständigt arbete`</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>`Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2218,10 +2369,15 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 1` ≠ kursplanens namn `Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning 1`</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>`Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2251,10 +2407,15 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 2` ≠ kursplanens namn `Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning 2`</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>`Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2284,10 +2445,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Programtext `Verksamhetsförlagd utbildning 3` ≠ kursplanens namn `Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+          <t>`Verksamhetsförlagd utbildning 3`</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>`Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2317,10 +2483,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Programtext `Didaktik och bedömning` ≠ kursplanens namn `Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+          <t>`Didaktik och bedömning`</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>`Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2350,10 +2521,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Programtext `Utveckling, lärande och ledarskap` ≠ kursplanens namn `Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+          <t>`Utveckling, lärande och ledarskap`</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>`Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2383,10 +2559,15 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Programtext `Sociala relationer, skolans historiska utveckling och samhällsuppdrag` ≠ kursplanens namn `Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
+          <t>`Sociala relationer, skolans historiska utveckling och samhällsuppdrag`</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>`Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
@@ -2411,7 +2592,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2419,7 +2600,12 @@
           <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>`Makroekonomi, introduktion` (kurskod `GNA3B8`)</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
@@ -2444,7 +2630,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2452,7 +2638,12 @@
           <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>`Mikroekonomi, introduktion` (kurskod `GNA3FN`)</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
@@ -2485,7 +2676,8 @@
           <t>`Evenemangsturism` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
@@ -2514,7 +2706,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2522,7 +2714,12 @@
           <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>`Makroekonomi, introduktion` (kurskod `GNA3B8`)</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2551,7 +2748,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2559,7 +2756,12 @@
           <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>`Mikroekonomi, introduktion` (kurskod `GNA3FN`)</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2588,7 +2790,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2798,12 @@
           <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>`Mikroekonomi, fortsättningskurs` (kurskod `NA1033`)</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2625,7 +2832,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2633,7 +2840,12 @@
           <t>`Makroekonomi fortsättning` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>`Makroekonomi, fortsättning` (kurskod `NA1036`)</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2662,7 +2874,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2670,7 +2882,12 @@
           <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt (Cost-Benefit Analysis)` (kurskod `NA2009`)</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
@@ -2695,7 +2912,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2703,7 +2920,12 @@
           <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>`Entreprenörskap - villkor och särart` (kurskod `EU1027`)</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
@@ -2728,7 +2950,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2958,12 @@
           <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>`Försäljnings-, förhandling- och dialogkonst` (kurskod `EU1034`)</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
@@ -2765,7 +2992,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2773,7 +3000,12 @@
           <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>`Studier i International Human Resource Management` (kurskod `FÖ3040`)</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
@@ -2806,7 +3038,8 @@
           <t>`Avancerad mikroteori` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
@@ -2831,7 +3064,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2839,7 +3072,12 @@
           <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt (Cost-Benefit Analysis)` (kurskod `NA2009`)</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
@@ -2872,7 +3110,8 @@
           <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2905,7 +3144,8 @@
           <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2935,10 +3175,11 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -2968,10 +3209,11 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3001,10 +3243,11 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3034,10 +3277,11 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3067,10 +3311,11 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
+          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3100,10 +3345,11 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3133,10 +3379,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
+          <t>`Vetenskap och metod` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3161,15 +3408,20 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr">
+          <t>`Personalarbete med praktik` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>`Personalarbete - med praktik` (kurskod `GAB3HQ`)</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
@@ -3202,7 +3454,8 @@
           <t>`Inriktning sociologi II` (30 hp)</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3235,7 +3488,8 @@
           <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3268,7 +3522,8 @@
           <t>`Makt och samhälle` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3301,7 +3556,8 @@
           <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3334,7 +3590,8 @@
           <t>`Inriktning statsvetenskap II` (30 hp)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3367,7 +3624,8 @@
           <t>`Inriktning sociologi III` (30 hp)</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3400,7 +3658,8 @@
           <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3433,7 +3692,8 @@
           <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3466,7 +3726,8 @@
           <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3499,7 +3760,8 @@
           <t>`Inriktning statsvetenskap III` (30 hp)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3524,15 +3786,16 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Kursraden ser avbruten/feltrycklig ut</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
+          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3557,15 +3820,20 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>`Samhällsvetenskapliga metoder II - inriktning statsvetenskap` (kurskod `GSK2PV`)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
@@ -3602,7 +3870,8 @@
           <t>`Festival och Event Management` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -3639,7 +3908,8 @@
           <t>`Turismstudier utomlands` (30 hp)</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
@@ -3676,201 +3946,202 @@
           <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G94"/>
+  <autoFilter ref="A1:H94"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
+++ b/vault-dalarna-university/03 IKS/Analys/Programkurser olänkade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Programkurser olänkade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$H$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Programkurser olänkade'!$A$1:$H$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>`Södra Afrikas moderna historia` (7 hp)</t>
+          <t>`Afrikas horn` (7 hp)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>`Afrikas horn` (7 hp)</t>
+          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -783,7 +783,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>`Fred och konflikt i Afrika: Internationell institutionell lag` (7 hp)</t>
+          <t>`Västafrika sedan 1800-talet` (7 hp)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -812,15 +812,19 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>`Västafrika sedan 1800-talet` (7 hp)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>`Magisterprojektets planering` (1 hp)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>`Afrikanska studier: Forskningsprojektets planering` (kurskod `AS3024`)</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
@@ -851,12 +855,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>`Magisterprojektets planering` (1 hp)</t>
+          <t>`Den vidareutvecklade uppsatsplanen` (1 hp)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>`Afrikanska studier: Forskningsprojektets planering` (kurskod `AS3024`)</t>
+          <t>`Afrikanska studier: Den vidareutvecklade forskningsplanen` (kurskod `AS3020`)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -889,12 +893,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>`Den vidareutvecklade uppsatsplanen` (1 hp)</t>
+          <t>`Islam och muslimska samhällen i Afrika` (7 hp)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>`Afrikanska studier: Den vidareutvecklade forskningsplanen` (kurskod `AS3020`)</t>
+          <t>`Afrikanska studier: Islam och islamiska samhällen i Afrika` (kurskod `AS3008`)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -906,7 +910,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>KFTPG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,10 +920,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2014-11-20</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>2014-03-19</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2021-03-23</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -927,24 +935,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>`Islam och muslimska samhällen i Afrika` (7 hp)</t>
+          <t>`Digitalefterbearbetning av ljud och bild` (15 hp)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>`Afrikanska studier: Islam och islamiska samhällen i Afrika` (kurskod `AS3008`)</t>
+          <t>`Digital efterbearbetning av ljud och bild` (kurskod `GBQ2AY`)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=HAFSA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KFTPG</t>
+          <t>KLJMG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -954,12 +962,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2014-03-19</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -969,17 +977,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>`Digitalefterbearbetning av ljud och bild` (15 hp)</t>
+          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>`Digital efterbearbetning av ljud och bild` (kurskod `GBQ2AY`)</t>
+          <t>`Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` (kurskod `GLP2NK`)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KFTPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1019,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion i Ljud- och musikproduktion` (7,5 hp)</t>
+          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>`Konceptutveckling inom medieproduktion för Ljud- och musikproduktion` (kurskod `GLP2NK`)</t>
+          <t>`Arbetsplatsförlagd utbildning i medieproduktion` (kurskod `GLP32S`)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1028,7 +1036,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KLJMG</t>
+          <t>KMLJG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1038,7 +1046,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
+          <t>2020-10-20</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1048,22 +1056,18 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>`Arbetsplatsförlagd utbildning för medieproduktion` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>`Arbetsplatsförlagd utbildning i medieproduktion` (kurskod `GLP32S`)</t>
-        </is>
-      </c>
+          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KLJMG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>`Audioteknologi I` (7,5 hp)</t>
+          <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>`Audioteknologi II` (7,5 hp)</t>
+          <t>`Vår tids musik och musikliv` (7,5 hp)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>`Introduktion till Musik- och ljuddesign` (7,5 hp)</t>
+          <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1209,7 +1213,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>`Ljudskapande och ljudsyntes` (7,5 hp)</t>
+          <t>`Musikbranschen` (7,5 hp)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1222,7 +1226,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1232,14 +1236,10 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -1247,20 +1247,20 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>`Vår tids musik och musikliv` (7,5 hp)</t>
+          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1270,14 +1270,10 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -1285,20 +1281,20 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>`Företagsekonomi för musikbranschen` (7,5 hp)</t>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KMLJG</t>
+          <t>L7I9A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1308,14 +1304,10 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2020-10-20</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>2023-07-05</t>
-        </is>
-      </c>
+          <t>2025-02-12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -1323,13 +1315,13 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>`Musikbranschen` (7,5 hp)</t>
+          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=KMLJG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
         </is>
       </c>
     </row>
@@ -1352,15 +1344,19 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare` (kurskod `APG24E`)</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
@@ -1386,15 +1382,19 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare årskurs 7–9 – AIL` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>`Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`)</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
@@ -1404,7 +1404,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1414,31 +1414,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 för ämneslärare årskurs 7–9 - AIL` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>`Didaktik och ledarskap i förskoleklass och grundskolans årskurs 1-3 (inkl 7,5 hp VFU)` (kurskod `GPG3CH`)</t>
+        </is>
+      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1448,31 +1456,39 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för ämneslärare årskurs 7–9 - AIL` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `APG275`)</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>L7I9A</t>
+          <t>LBF3A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1482,10 +1498,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -1493,17 +1513,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>`_Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7–9` (15 hp)</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3`</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>`Examensarbete i matematik för ämneslärarexamen inriktning grundskolans årskurs 7-9` (kurskod `AMD239`)</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=L7I9A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1555,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
+          <t>`Engelska för grundlärare åk F-3`</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap i förskoleklass och grundskolans årskurs 1-3 (inkl 7,5 hp VFU)` (kurskod `GPG3CH`)</t>
+          <t>`Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1552,7 +1572,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1562,12 +1582,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1577,24 +1597,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1–3` (15 hp)</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i förskoleklass och grundskolans åk 1-3 (varav 7,5 hp VFU)` (kurskod `APG275`)</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1604,12 +1624,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1619,24 +1639,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F -3`</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning för grundlärare F-3` (kurskod `APG244`)</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LBF3A</t>
+          <t>LP79A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1646,12 +1666,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2020-12-17</t>
+          <t>2017-12-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2023-06-02</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1661,17 +1681,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare åk F-3`</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>`Engelska för grundlärare F-3` (kurskod `GEN2BJ`)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LBF3A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
         </is>
       </c>
     </row>
@@ -1698,15 +1718,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
@@ -1736,7 +1760,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1744,7 +1768,11 @@
           <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>`Verksamhetsförlagd utbildning i grundskolan årskurs 7-9` (kurskod `APG28S`)</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
@@ -1754,7 +1782,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1779,24 +1807,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9` (15 hp)</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande för ämneslärare inriktning åk 7-9 (varav 7,5 hp VFU)` (kurskod `GPG328`)</t>
+          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)` (kurskod `GPG3KB`)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1821,24 +1849,24 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+          <t>`Utveckling och lärande för ämneslärare inriktning gymnasieskolan (varav 7,5 hp VFU)` (kurskod `GPG329`)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>LP79A</t>
+          <t>LPGYA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1863,17 +1891,17 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LP79A</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
         </is>
       </c>
     </row>
@@ -1900,15 +1928,19 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - ämneslärare` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
@@ -1938,7 +1970,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1946,7 +1978,11 @@
           <t>`Verksamhetsförlagd utbildning - ämneslärare` (15 hp)</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>`Verksamhetsförlagd utbildning i gymnasieskolan` (kurskod `APG28R`)</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
@@ -1956,7 +1992,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1966,14 +2002,10 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -1981,24 +2013,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan` (15 hp)</t>
+          <t>`Skolans samhällsuppdrag`</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap för ämneslärare inriktning gymnasieskolan (inkl 7,5 hp VFU)` (kurskod `GPG3KB`)</t>
+          <t>`Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2008,14 +2040,10 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -2023,24 +2051,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt - ämneslärare` (7,5 hp)</t>
+          <t>`Didaktik och ledarskap`</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>`Sociala relationer, konflikter och makt i grundskolan åk 7-9 och gymnasieskolan` (kurskod `GPG2S9`)</t>
+          <t>`Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>LPGYA</t>
+          <t>LVALA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2050,14 +2078,10 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2017-12-19</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -2065,17 +2089,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete för ämneslärare` (7,5 hp)</t>
+          <t>`Utveckling och lärande`</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete i grundskolans åk 7-9 och gymnasieskolan` (kurskod `APG24S`)</t>
+          <t>`Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LPGYA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2127,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>`Skolans samhällsuppdrag`</t>
+          <t>`Sociala relationer och konflikthantering`</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>`Skolans samhällsuppdrag - VAL` (kurskod `GPG2Z7`)</t>
+          <t>`Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2141,12 +2165,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap`</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning`</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>`Didaktik och ledarskap - VAL` (kurskod `GPG3BE`)</t>
+          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2179,12 +2203,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande`</t>
+          <t>`Utvärdering och utvecklingsarbete`</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>`Utveckling och lärande - VAL` (kurskod `GPG2Z4`)</t>
+          <t>`Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2217,12 +2241,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>`Sociala relationer och konflikthantering`</t>
+          <t>`Självständigt arbete`</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>`Sociala relationer och konflikthantering - VAL` (kurskod `GPG2Z6`)</t>
+          <t>`Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2255,12 +2279,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning`</t>
+          <t>`Verksamhetsförlagd utbildning 1`</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>`Vetenskapsteori och utbildningsvetenskaplig forskning - VAL` (kurskod `APG28M`)</t>
+          <t>`Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2293,12 +2317,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete`</t>
+          <t>`Verksamhetsförlagd utbildning 2`</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>`Utvärdering och utvecklingsarbete - VAL` (kurskod `GPG3FU`)</t>
+          <t>`Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2331,12 +2355,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>`Självständigt arbete`</t>
+          <t>`Verksamhetsförlagd utbildning 3`</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>`Självständigt arbete - VAL` (kurskod `GPG3FV`)</t>
+          <t>`Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2369,12 +2393,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 1`</t>
+          <t>`Didaktik och bedömning`</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 1 - VAL` (kurskod `GPG3FS`)</t>
+          <t>`Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2407,12 +2431,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 2`</t>
+          <t>`Utveckling, lärande och ledarskap`</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 2 - VAL` (kurskod `GPG3FT`)</t>
+          <t>`Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -2445,12 +2469,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3`</t>
+          <t>`Sociala relationer, skolans historiska utveckling och samhällsuppdrag`</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>`Verksamhetsförlagd utbildning 3 - VAL` (kurskod `APG2BK`)</t>
+          <t>`Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2462,7 +2486,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2472,7 +2496,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2483,24 +2507,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>`Didaktik och bedömning`</t>
+          <t>`Makroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>`Didaktik och bedömning - VAL` (kurskod `GPG33F`)</t>
+          <t>`Makroekonomi, introduktion` (kurskod `GNA3B8`)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SBMPG</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2510,7 +2534,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2521,24 +2545,24 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>`Utveckling, lärande och ledarskap`</t>
+          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>`Utveckling, lärande och ledarskap - VAL` (kurskod `GPG33D`)</t>
+          <t>`Mikroekonomi, introduktion` (kurskod `GNA3FN`)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LVALA</t>
+          <t>SDUVA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2548,35 +2572,31 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2012-05-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>`Sociala relationer, skolans historiska utveckling och samhällsuppdrag`</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>`Sociala relationer, skolans historiska utveckling och samhällsuppdrag - VAL` (kurskod `GPG33E`)</t>
-        </is>
-      </c>
+          <t>`Evenemangsturism` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=LVALA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2586,10 +2606,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -2607,14 +2631,14 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>SBMPG</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2624,10 +2648,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -2645,14 +2673,14 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SBMPG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SDUVA</t>
+          <t>SENGR</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2662,24 +2690,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2012-05-02</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>2023-02-24</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>`Evenemangsturism` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+          <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>`Mikroekonomi, fortsättningskurs` (kurskod `NA1033`)</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SDUVA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
         </is>
       </c>
     </row>
@@ -2711,12 +2747,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>`Makroekonomi introduktion` (7,5 hp)</t>
+          <t>`Makroekonomi fortsättning` (7,5 hp)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>`Makroekonomi, introduktion` (kurskod `GNA3B8`)</t>
+          <t>`Makroekonomi, fortsättning` (kurskod `NA1036`)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -2753,12 +2789,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>`Mikroekonomi introduktion` (7,5 hp)</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>`Mikroekonomi, introduktion` (kurskod `GNA3FN`)</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt (Cost-Benefit Analysis)` (kurskod `NA2009`)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -2770,7 +2806,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2780,14 +2816,10 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -2795,24 +2827,24 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>`Mikroekonomi fortsättningskurs` (7,5 hp)</t>
+          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>`Mikroekonomi, fortsättningskurs` (kurskod `NA1033`)</t>
+          <t>`Entreprenörskap - villkor och särart` (kurskod `EU1027`)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SEPFG</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2822,14 +2854,10 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
+          <t>2024-03-12</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>Programtext avviker från kursplanens namn</t>
@@ -2837,24 +2865,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>`Makroekonomi fortsättning` (7,5 hp)</t>
+          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>`Makroekonomi, fortsättning` (kurskod `NA1036`)</t>
+          <t>`Försäljnings-, förhandling- och dialogkonst` (kurskod `EU1034`)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SENGR</t>
+          <t>SFIFA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2864,12 +2892,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2023-02-24</t>
+          <t>2017-09-14</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2879,24 +2907,24 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
+          <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt (Cost-Benefit Analysis)` (kurskod `NA2009`)</t>
+          <t>`Studier i International Human Resource Management` (kurskod `FÖ3040`)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SENGR</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2906,35 +2934,31 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>`Entreprenörskap - entreprenörskapets villkor och särart` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>`Entreprenörskap - villkor och särart` (kurskod `EU1027`)</t>
-        </is>
-      </c>
+          <t>`Avancerad mikroteori` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SEPFG</t>
+          <t>SMINA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2944,7 +2968,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-03-12</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2955,24 +2979,24 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>`Förhandlings  försäljnings  och dialogkonst` (7,5 hp)</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>`Försäljnings-, förhandling- och dialogkonst` (kurskod `EU1034`)</t>
+          <t>`Samhällsekonomisk utvärdering av offentliga projekt (Cost-Benefit Analysis)` (kurskod `NA2009`)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SEPFG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SFIFA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2982,39 +3006,31 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2017-09-14</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>`Studier i Internationell Human Resource Management` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>`Studier i International Human Resource Management` (kurskod `FÖ3040`)</t>
-        </is>
-      </c>
+          <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SFIFA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3024,7 +3040,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -3035,20 +3051,20 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>`Avancerad mikroteori` (7,5 hp)</t>
+          <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SMINA</t>
+          <t>SPARG</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -3058,28 +3074,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>`Samhällsekonomisk utvärdering av offentliga projekt (Cost-Benefit Analysis)` (kurskod `NA2009`)</t>
-        </is>
-      </c>
+          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SMINA</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3119,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>`Arbetsrätt i personalarbetets praktik` (15 hp)</t>
+          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -3141,7 +3153,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>`Grunder i personalekonomisk styrning` (15 hp)</t>
+          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3175,7 +3187,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>`Arbetsmarknad i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3209,7 +3221,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>`Arbetsmiljökunskap i ett jämförande internationellt perspektiv` (7,5 hp)</t>
+          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -3243,7 +3255,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>`Examensarbete inom arbetsvetenskap` (15 hp)</t>
+          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -3277,7 +3289,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>`Forskningsprocess och analysmetoder` (7,5 hp)</t>
+          <t>`Vetenskap och metod` (7,5 hp)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -3306,15 +3318,19 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>`Komplexa arbetsorganisationer` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
+          <t>`Personalarbete med praktik` (15 hp)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>`Personalarbete - med praktik` (kurskod `GAB3HQ`)</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
@@ -3324,7 +3340,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3334,7 +3350,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3345,20 +3361,20 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>`Komplexa sociala processer i arbetslivet` (7,5 hp)</t>
+          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3368,7 +3384,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3379,20 +3395,20 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>`Vetenskap och metod` (7,5 hp)</t>
+          <t>`Makt och samhälle` (7,5 hp)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SPARG</t>
+          <t>SSHVG</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3402,28 +3418,24 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Programtext avviker från kursplanens namn</t>
+          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>`Personalarbete med praktik` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>`Personalarbete - med praktik` (kurskod `GAB3HQ`)</t>
-        </is>
-      </c>
+          <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SPARG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3463,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi II` (30 hp)</t>
+          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -3485,7 +3497,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>`Examensarbete för högskoleexamen i Sociologi` (7,5 hp)</t>
+          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -3519,7 +3531,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>`Makt och samhälle` (7,5 hp)</t>
+          <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3548,15 +3560,19 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
+          <t>Programtext avviker från kursplanens namn</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>`Samhällsvetenskapliga metoder I` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
+          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>`Samhällsvetenskapliga metoder II - inriktning statsvetenskap` (kurskod `GSK2PV`)</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
@@ -3566,7 +3582,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3576,10 +3592,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -3587,20 +3607,20 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>`Inriktning statsvetenskap II` (30 hp)</t>
+          <t>`Festival och Event Management` (7,5 hp)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
+          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>SSHVG</t>
+          <t>STMGG</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3610,10 +3630,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>2017-11-15</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>Kursnamnet finns varken aktivt eller nedlagt</t>
@@ -3621,340 +3645,18 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>`Inriktning sociologi III` (30 hp)</t>
+          <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>`Examensarbete för kandidatexamen i sociologi` (15 hp)</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>`Fördjupningskurs i sociologisk teori` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>`Inriktning statsvetenskap III` (30 hp)</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Kursraden ser avbruten/feltrycklig ut</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>`Valbar termin (med möjlighet till internationellt utbyte eller läsning av valfri temakurs/kurser om` (30 hp)</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>SSHVG</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2021-06-16</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Programtext avviker från kursplanens namn</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II inriktning statsvetenskap` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>`Samhällsvetenskapliga metoder II - inriktning statsvetenskap` (kurskod `GSK2PV`)</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=SSHVG</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>`Festival och Event Management` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>`Turismstudier utomlands` (30 hp)</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>STMGG</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Utbildningsplan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2017-11-15</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2023-03-17</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Kursnamnet finns varken aktivt eller nedlagt</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>`Kvantitativa forskningsmetoder` (7,5 hp)</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/Program/utbildningsplan/?code=STMGG</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H94"/>
+  <autoFilter ref="A1:H85"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId2"/>
@@ -4124,24 +3826,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId186"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
